--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487829_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487829_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.5107</v>
+        <v>9.414099999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0705</v>
+        <v>4.8858</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4403</v>
+        <v>4.5283</v>
       </c>
       <c r="G2" t="n">
         <v>7.0852</v>
@@ -610,13 +610,13 @@
         <v>3.7461</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.28</v>
+        <v>-0.3766</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2396</v>
+        <v>-0.4243</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0404</v>
+        <v>0.0477</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8502</v>
+        <v>6.4028</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1847</v>
+        <v>2.6786</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6656</v>
+        <v>3.7243</v>
       </c>
       <c r="G3" t="n">
         <v>2.0062</v>
@@ -688,13 +688,13 @@
         <v>3.538</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0915</v>
+        <v>-0.5389</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0315</v>
+        <v>-0.5376</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.06</v>
+        <v>-0.0012</v>
       </c>
       <c r="V3" t="n">
         <v>1.3975</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.8493</v>
+        <v>6.3828</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5248</v>
+        <v>3.9115</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3246</v>
+        <v>2.4714</v>
       </c>
       <c r="G4" t="n">
         <v>4.0117</v>
@@ -766,13 +766,13 @@
         <v>3.1218</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9303</v>
+        <v>-0.3968</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.46</v>
+        <v>-0.0733</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4703</v>
+        <v>-0.3235</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3538</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.799</v>
+        <v>5.6961</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7435</v>
+        <v>3.5525</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0555</v>
+        <v>2.1435</v>
       </c>
       <c r="G5" t="n">
         <v>1.3898</v>
@@ -844,13 +844,13 @@
         <v>3.3299</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5689</v>
+        <v>-0.6718</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0058</v>
+        <v>-0.1852</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5747</v>
+        <v>-0.4866</v>
       </c>
       <c r="V5" t="n">
         <v>2.6889</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.4128</v>
+        <v>3.6337</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7619</v>
+        <v>2.0415</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6509</v>
+        <v>1.5922</v>
       </c>
       <c r="G6" t="n">
         <v>2.996</v>
@@ -922,13 +922,13 @@
         <v>1.4568</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4802</v>
+        <v>-0.2593</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5219</v>
+        <v>-0.2424</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0418</v>
+        <v>-0.0169</v>
       </c>
       <c r="V6" t="n">
         <v>1.5213</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7382</v>
+        <v>2.1781</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.2719</v>
+        <v>-2.4209</v>
       </c>
       <c r="F7" t="n">
-        <v>5.01</v>
+        <v>4.599</v>
       </c>
       <c r="G7" t="n">
         <v>0.4157</v>
@@ -1000,13 +1000,13 @@
         <v>3.9542</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3256</v>
+        <v>-0.2345</v>
       </c>
       <c r="T7" t="n">
-        <v>0.07099999999999999</v>
+        <v>-0.078</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2545</v>
+        <v>-0.1565</v>
       </c>
       <c r="V7" t="n">
         <v>0.1238</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.493</v>
+        <v>1.6757</v>
       </c>
       <c r="E8" t="n">
-        <v>0.213</v>
+        <v>0.2782</v>
       </c>
       <c r="F8" t="n">
-        <v>1.28</v>
+        <v>1.3975</v>
       </c>
       <c r="G8" t="n">
         <v>2.2254</v>
@@ -1078,13 +1078,13 @@
         <v>3.7461</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5867</v>
+        <v>-1.404</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3824</v>
+        <v>-0.3171</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.2043</v>
+        <v>-1.0868</v>
       </c>
       <c r="V8" t="n">
         <v>0.23</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. GARCIA-ABRIL GUERRERO</t>
+          <t>P. MARIN FONTAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1969</v>
+        <v>-0.2765</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4033</v>
+        <v>-2.9212</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6002</v>
+        <v>2.6448</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.1495</v>
+        <v>-1.5719</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.1217</v>
+        <v>-1.2151</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0278</v>
+        <v>-0.3568</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.7452</v>
+        <v>-1.343</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.1092</v>
+        <v>-0.4841</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.636</v>
+        <v>-0.8589</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4043</v>
+        <v>-0.2289</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0126</v>
+        <v>-0.731</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6082</v>
+        <v>0.5021</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8325</v>
+        <v>1.8731</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8731</v>
+        <v>2.9137</v>
       </c>
       <c r="S9" t="n">
-        <v>3.1778</v>
+        <v>-1.2853</v>
       </c>
       <c r="T9" t="n">
-        <v>1.8788</v>
+        <v>-0.5376</v>
       </c>
       <c r="U9" t="n">
-        <v>1.299</v>
+        <v>-0.7476</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3361</v>
+        <v>0.7076</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5036</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1675</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="10">
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. HANSEN GUTIERREZ</t>
+          <t>J. GARCIA-ABRIL GUERRERO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8389</v>
+        <v>-0.7268</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8257</v>
+        <v>-1.9454</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0132</v>
+        <v>1.2185</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6503</v>
+        <v>-3.1495</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7932</v>
+        <v>-3.1217</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1429</v>
+        <v>-0.0278</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6952</v>
+        <v>-2.7452</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6952</v>
+        <v>-2.1092</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0.636</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0449</v>
+        <v>-0.4043</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.098</v>
+        <v>-1.0126</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1429</v>
+        <v>0.6082</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2081</v>
+        <v>0.8325</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2081</v>
+        <v>1.8731</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3967</v>
+        <v>1.2541</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1305</v>
+        <v>0.3367</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2662</v>
+        <v>0.9173</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.3361</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.5036</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. MARIN FONTAN</t>
+          <t>I. HANSEN GUTIERREZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0933</v>
+        <v>-0.8095</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4151</v>
+        <v>-0.8257</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3218</v>
+        <v>0.0162</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.5719</v>
+        <v>-0.6503</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2151</v>
+        <v>-0.7932</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3568</v>
+        <v>0.1429</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.343</v>
+        <v>-0.6952</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4841</v>
+        <v>-0.6952</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.8589</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2289</v>
+        <v>0.0449</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.731</v>
+        <v>-0.098</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5021</v>
+        <v>0.1429</v>
       </c>
       <c r="P12" t="n">
-        <v>1.8731</v>
+        <v>0.2081</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.9137</v>
+        <v>0.2081</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.1021</v>
+        <v>-0.3673</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0315</v>
+        <v>-0.1305</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0706</v>
+        <v>-0.2368</v>
       </c>
       <c r="V12" t="n">
-        <v>0.7076</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.7076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>32.36559999999999</v>
+        <v>33.0182</v>
       </c>
       <c r="E13" t="n">
-        <v>7.822</v>
+        <v>8.474500000000001</v>
       </c>
       <c r="F13" t="n">
         <v>24.5438</v>
@@ -1435,7 +1435,7 @@
         <v>14.206</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4901000000000009</v>
+        <v>0.4901000000000001</v>
       </c>
       <c r="I13" t="n">
         <v>13.7159</v>
@@ -1450,13 +1450,13 @@
         <v>5.3066</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8753000000000001</v>
+        <v>0.8753000000000002</v>
       </c>
       <c r="N13" t="n">
         <v>-7.534</v>
       </c>
       <c r="O13" t="n">
-        <v>8.4094</v>
+        <v>8.409399999999998</v>
       </c>
       <c r="P13" t="n">
         <v>16.6495</v>
@@ -1465,16 +1465,16 @@
         <v>-11.4466</v>
       </c>
       <c r="R13" t="n">
-        <v>28.0959</v>
+        <v>28.09590000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.141100000000001</v>
+        <v>-4.4885</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.907</v>
+        <v>-2.2545</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.2341</v>
+        <v>-2.2338</v>
       </c>
       <c r="V13" t="n">
         <v>6.6514</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. MARTINEZ MEGIAS</t>
+          <t>A. CAÑETE PUENTENUEVA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0819</v>
+        <v>1.0279</v>
       </c>
       <c r="E14" t="n">
-        <v>1.636</v>
+        <v>-0.0284</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4459</v>
+        <v>1.0562</v>
       </c>
       <c r="G14" t="n">
-        <v>1.05</v>
+        <v>0.3678</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2067</v>
+        <v>0.8658</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8434</v>
+        <v>-0.498</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5156</v>
+        <v>0.3026</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8885999999999999</v>
+        <v>1.017</v>
       </c>
       <c r="L14" t="n">
-        <v>0.627</v>
+        <v>-0.7144</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4656</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.1512</v>
       </c>
       <c r="O14" t="n">
         <v>0.2164</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.1218</v>
+        <v>1.0406</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.1624</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>1.0406</v>
       </c>
       <c r="S14" t="n">
-        <v>3.8622</v>
+        <v>-0.3805</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1152</v>
+        <v>-0.331</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7471</v>
+        <v>-0.0496</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2914</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1238</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. CAÑETE PUENTENUEVA</t>
+          <t>J. MARTINEZ MEGIAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4715</v>
+        <v>0.8365</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3498</v>
+        <v>-0.4</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8214</v>
+        <v>1.2365</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3678</v>
+        <v>1.05</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8658</v>
+        <v>0.2067</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.498</v>
+        <v>0.8434</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3026</v>
+        <v>1.5156</v>
       </c>
       <c r="K15" t="n">
-        <v>1.017</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.7144</v>
+        <v>0.627</v>
       </c>
       <c r="M15" t="n">
-        <v>0.06519999999999999</v>
+        <v>-0.4656</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1512</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="O15" t="n">
         <v>0.2164</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-4.1624</v>
       </c>
       <c r="R15" t="n">
         <v>1.0406</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9369</v>
+        <v>1.6168</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6524</v>
+        <v>1.0792</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2844</v>
+        <v>0.5376</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.2914</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.1238</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.1507</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0903</v>
+        <v>-1.1974</v>
       </c>
       <c r="F16" t="n">
-        <v>1.172</v>
+        <v>1.3482</v>
       </c>
       <c r="G16" t="n">
         <v>1.5329</v>
@@ -1702,13 +1702,13 @@
         <v>1.0406</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4032</v>
+        <v>0.4722</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0033</v>
+        <v>-0.1105</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4065</v>
+        <v>0.5826</v>
       </c>
       <c r="V16" t="n">
         <v>-0.8137</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2168</v>
+        <v>-0.4796</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2232</v>
+        <v>-0.5446</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0064</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0726</v>
@@ -1780,13 +1780,13 @@
         <v>0.2081</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6883</v>
+        <v>0.4255</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6491</v>
+        <v>0.3277</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0391</v>
+        <v>0.0979</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.944</v>
+        <v>-0.963</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6223</v>
+        <v>0.5151</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5662</v>
+        <v>-1.4782</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5495</v>
@@ -1858,13 +1858,13 @@
         <v>0.2081</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5839</v>
+        <v>0.4767</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0189</v>
+        <v>0.0692</v>
       </c>
       <c r="V18" t="n">
         <v>-1.1675</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. FAIAL</t>
+          <t>G. BOAHEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5913</v>
+        <v>-1.32</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0854</v>
+        <v>1.2346</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5059</v>
+        <v>-2.5546</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0467</v>
+        <v>2.1947</v>
       </c>
       <c r="H19" t="n">
-        <v>2.0682</v>
+        <v>1.953</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.0215</v>
+        <v>0.2417</v>
       </c>
       <c r="J19" t="n">
-        <v>2.2881</v>
+        <v>4.0972</v>
       </c>
       <c r="K19" t="n">
-        <v>3.138</v>
+        <v>2.9698</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.8499</v>
+        <v>1.1275</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.2414</v>
+        <v>-1.9025</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0699</v>
+        <v>-1.0167</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1716</v>
+        <v>-0.8858</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.9137</v>
+        <v>-1.6649</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.1624</v>
+        <v>-3.1218</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2487</v>
+        <v>1.4568</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4143</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.901</v>
+        <v>0.2591</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4868</v>
+        <v>0.4561</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6899</v>
+        <v>-2.565</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6899</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.565</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. LOPES MARQUES</t>
+          <t>L. FAIAL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6732</v>
+        <v>-1.4253</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6728</v>
+        <v>-1.1209</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0004</v>
+        <v>-0.3044</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4371</v>
+        <v>0.0467</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5222</v>
+        <v>2.0682</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9593</v>
+        <v>-2.0215</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4325</v>
+        <v>2.2881</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4325</v>
+        <v>3.138</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.8499</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8696</v>
+        <v>-2.2414</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0897</v>
+        <v>-1.0699</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9593</v>
+        <v>-1.1716</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2081</v>
+        <v>-2.9137</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0406</v>
+        <v>-4.1624</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2009</v>
+        <v>0.7517</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0033</v>
+        <v>0.0634</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2042</v>
+        <v>0.6884</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.2289</v>
+        <v>0.6899</v>
       </c>
       <c r="W20" t="n">
-        <v>-1.0614</v>
+        <v>0.6899</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. BOAHEN</t>
+          <t>A. LOPES MARQUES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.809</v>
+        <v>-3.024</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2702</v>
+        <v>-1.9943</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.0792</v>
+        <v>-1.0297</v>
       </c>
       <c r="G21" t="n">
-        <v>2.1947</v>
+        <v>-0.4371</v>
       </c>
       <c r="H21" t="n">
-        <v>1.953</v>
+        <v>0.5222</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2417</v>
+        <v>-0.9593</v>
       </c>
       <c r="J21" t="n">
-        <v>4.0972</v>
+        <v>0.4325</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9698</v>
+        <v>0.4325</v>
       </c>
       <c r="L21" t="n">
-        <v>1.1275</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9025</v>
+        <v>-0.8696</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0167</v>
+        <v>0.0897</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8858</v>
+        <v>-0.9593</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.6649</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4568</v>
+        <v>0.8325</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7738</v>
+        <v>-0.1499</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7053</v>
+        <v>-0.3248</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.1749</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.565</v>
+        <v>-2.2289</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-1.0614</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.565</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4849</v>
+        <v>-4.0269</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1646</v>
+        <v>-1.7359</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3204</v>
+        <v>-2.291</v>
       </c>
       <c r="G22" t="n">
         <v>-4.284</v>
@@ -2170,13 +2170,13 @@
         <v>0.6244</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8253</v>
+        <v>-0.3673</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5219</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3033</v>
+        <v>-0.274</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.157</v>
+        <v>-5.4886</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.9276</v>
+        <v>-4.2846</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2294</v>
+        <v>-1.204</v>
       </c>
       <c r="G23" t="n">
         <v>-3.9791</v>
@@ -2248,13 +2248,13 @@
         <v>1.4568</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3008</v>
+        <v>0.9692</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2519</v>
+        <v>0.3911</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5527</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-0.8137</v>
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.4004</v>
+        <v>-7.9362</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.073600000000001</v>
+        <v>-8.609400000000001</v>
       </c>
       <c r="F24" t="n">
         <v>0.6732</v>
@@ -2326,10 +2326,10 @@
         <v>1.0406</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7144</v>
+        <v>0.1786</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5276999999999999</v>
+        <v>-0.008</v>
       </c>
       <c r="U24" t="n">
         <v>0.1866</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.724299999999999</v>
+        <v>-9.002800000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.485</v>
+        <v>-6.3778</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.2393</v>
+        <v>-2.6249</v>
       </c>
       <c r="G25" t="n">
         <v>-6.4564</v>
@@ -2404,13 +2404,13 @@
         <v>1.2487</v>
       </c>
       <c r="S25" t="n">
-        <v>1.3564</v>
+        <v>1.078</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3972</v>
+        <v>0.5044</v>
       </c>
       <c r="U25" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.5736</v>
       </c>
       <c r="V25" t="n">
         <v>-1.7513</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-32.3658</v>
+        <v>-31.6513</v>
       </c>
       <c r="E26" t="n">
-        <v>-24.5438</v>
+        <v>-24.5436</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.821899999999999</v>
+        <v>-7.1076</v>
       </c>
       <c r="G26" t="n">
         <v>-14.206</v>
@@ -2482,13 +2482,13 @@
         <v>11.4465</v>
       </c>
       <c r="S26" t="n">
-        <v>5.1409</v>
+        <v>5.8554</v>
       </c>
       <c r="T26" t="n">
         <v>2.234</v>
       </c>
       <c r="U26" t="n">
-        <v>2.9071</v>
+        <v>3.6214</v>
       </c>
       <c r="V26" t="n">
         <v>-6.651199999999999</v>
